--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122457834</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98086</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>233</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calypso bulbosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Backträsk, Altersbruk, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>790136</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7285517</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>BD-Pit-0003</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sluttning med blandskog, nära bäck</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Allis Zethraeus, Ulf Zethraeus</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457834</v>
+        <v>122457833</v>
       </c>
       <c r="B3" t="n">
         <v>98086</v>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sluttning med blandskog, nära bäck</t>
+          <t>frisk blandskog i svag sluttning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Allis Zethraeus, Ulf Zethraeus</t>
+          <t>Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122457833</v>
       </c>
       <c r="B3" t="n">
-        <v>98086</v>
+        <v>98091</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122457833</v>
       </c>
       <c r="B3" t="n">
-        <v>98091</v>
+        <v>98100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,11 +817,6 @@
       </c>
       <c r="E3" t="n">
         <v>233</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457833</v>
+        <v>122457834</v>
       </c>
       <c r="B3" t="n">
-        <v>98100</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,6 +817,11 @@
       </c>
       <c r="E3" t="n">
         <v>233</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norna</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -874,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>frisk blandskog i svag sluttning</t>
+          <t>sluttning med blandskog, nära bäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Zethraeus</t>
+          <t>Allis Zethraeus, Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122457834</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Allis Zethraeus, Ulf Zethraeus</t>
+          <t>Ulf Zethraeus, Allis Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457834</v>
+        <v>122457833</v>
       </c>
       <c r="B3" t="n">
         <v>98126</v>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sluttning med blandskog, nära bäck</t>
+          <t>frisk blandskog i svag sluttning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Zethraeus, Allis Zethraeus</t>
+          <t>Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457833</v>
+        <v>122457834</v>
       </c>
       <c r="B3" t="n">
-        <v>98126</v>
+        <v>98129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>frisk blandskog i svag sluttning</t>
+          <t>sluttning med blandskog, nära bäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Zethraeus</t>
+          <t>Allis Zethraeus, Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122457834</v>
       </c>
       <c r="B3" t="n">
-        <v>98129</v>
+        <v>98130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457834</v>
+        <v>122457833</v>
       </c>
       <c r="B3" t="n">
-        <v>98130</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sluttning med blandskog, nära bäck</t>
+          <t>frisk blandskog i svag sluttning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Allis Zethraeus, Ulf Zethraeus</t>
+          <t>Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457833</v>
+        <v>122457834</v>
       </c>
       <c r="B3" t="n">
         <v>98133</v>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>frisk blandskog i svag sluttning</t>
+          <t>sluttning med blandskog, nära bäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Zethraeus</t>
+          <t>Allis Zethraeus, Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122457834</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122457834</v>
+        <v>122457833</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,17 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>450 m O-ONO om Backträskets norra spets, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
+          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sluttning med blandskog, nära bäck</t>
+          <t>frisk blandskog i svag sluttning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Allis Zethraeus, Ulf Zethraeus</t>
+          <t>Ulf Zethraeus</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,132 +793,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>122457833</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>233</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Backträsk, Altersbruk, Nb</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>790136</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7285517</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>BD-Pit-0003</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2000-06-10</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2000-06-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lövgrensbäcken, 50 m O om bäck- och vägkorsningen, södra sidan av bäcken, Obskoord: 7284355/1753255/100 m (Avst fr FV-lokal: 57 m). Norrbottens flora - 2010.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>frisk blandskog i svag sluttning</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Ulf Zethraeus</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98903</v>
+        <v>98904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98904</v>
+        <v>98907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98907</v>
+        <v>98908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98908</v>
+        <v>98910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98910</v>
+        <v>98911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6763777</v>
       </c>
       <c r="B2" t="n">
-        <v>98911</v>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9007-2024 artfynd.xlsx
+++ b/artfynd/A 9007-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,8 +796,16 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6763777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>